--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F388"/>
+  <dimension ref="A1:F389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9744,6 +9744,30 @@
         <v>388.24</v>
       </c>
       <c r="F388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>362.94</v>
+      </c>
+      <c r="C389" t="n">
+        <v>374.09</v>
+      </c>
+      <c r="D389" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="E389" t="n">
+        <v>388</v>
+      </c>
+      <c r="F389" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9760,7 +9784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B413"/>
+  <dimension ref="A1:B415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13893,6 +13917,26 @@
       </c>
       <c r="B413" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>-0.96</v>
       </c>
     </row>
   </sheetData>
@@ -14061,28 +14105,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03928250091464607</v>
+        <v>0.03618378229294905</v>
       </c>
       <c r="J2" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K2" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007014980965515893</v>
+        <v>0.005945041904207526</v>
       </c>
       <c r="M2" t="n">
-        <v>2.862682963592673</v>
+        <v>2.870381967609242</v>
       </c>
       <c r="N2" t="n">
-        <v>12.31475646447359</v>
+        <v>12.37963581179123</v>
       </c>
       <c r="O2" t="n">
-        <v>3.509238730048668</v>
+        <v>3.518470663767318</v>
       </c>
       <c r="P2" t="n">
-        <v>368.0299242859965</v>
+        <v>368.0630200351598</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14139,28 +14183,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02849554002364505</v>
+        <v>0.02668652914187647</v>
       </c>
       <c r="J3" t="n">
+        <v>388</v>
+      </c>
+      <c r="K3" t="n">
         <v>387</v>
       </c>
-      <c r="K3" t="n">
-        <v>386</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.004607927717996341</v>
+        <v>0.00405285736931893</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6025553010054</v>
+        <v>2.60427837131423</v>
       </c>
       <c r="N3" t="n">
-        <v>9.912202989423971</v>
+        <v>9.91962364174015</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14836512962267</v>
+        <v>3.149543402104526</v>
       </c>
       <c r="P3" t="n">
-        <v>376.9099509708942</v>
+        <v>376.9292563535164</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14217,28 +14261,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06748449578318577</v>
+        <v>0.06674043710193092</v>
       </c>
       <c r="J4" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K4" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02389619155932832</v>
+        <v>0.02350051756153781</v>
       </c>
       <c r="M4" t="n">
-        <v>2.403528356095898</v>
+        <v>2.401272813001441</v>
       </c>
       <c r="N4" t="n">
-        <v>10.48785563212204</v>
+        <v>10.46639577905257</v>
       </c>
       <c r="O4" t="n">
-        <v>3.238495890397584</v>
+        <v>3.235180949970584</v>
       </c>
       <c r="P4" t="n">
-        <v>384.8140596666208</v>
+        <v>384.8220065577341</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14295,28 +14339,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0589318114614227</v>
+        <v>0.05884423973049724</v>
       </c>
       <c r="J5" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K5" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01613632785665697</v>
+        <v>0.01617803150996089</v>
       </c>
       <c r="M5" t="n">
-        <v>2.62119825156036</v>
+        <v>2.614888170124066</v>
       </c>
       <c r="N5" t="n">
-        <v>11.93826368280471</v>
+        <v>11.90757212752555</v>
       </c>
       <c r="O5" t="n">
-        <v>3.455179254800641</v>
+        <v>3.450735012649559</v>
       </c>
       <c r="P5" t="n">
-        <v>386.5912555023473</v>
+        <v>386.5921908089673</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14354,7 +14398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F388"/>
+  <dimension ref="A1:F389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26769,6 +26813,38 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>-35.42906897335555,174.43148048941072</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>-35.42977073051901,174.43127817525013</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-35.43046398381929,174.43121542132187</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-35.431140968528815,174.43135879972124</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F389"/>
+  <dimension ref="A1:F392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9770,6 +9770,78 @@
       <c r="F389" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>360.84</v>
+      </c>
+      <c r="C390" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="D390" t="n">
+        <v>384.12</v>
+      </c>
+      <c r="E390" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>361.24</v>
+      </c>
+      <c r="C391" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="D391" t="n">
+        <v>384.27</v>
+      </c>
+      <c r="E391" t="n">
+        <v>388.37</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>361.59</v>
+      </c>
+      <c r="C392" t="n">
+        <v>373.81</v>
+      </c>
+      <c r="D392" t="n">
+        <v>383.82</v>
+      </c>
+      <c r="E392" t="n">
+        <v>388.65</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B415"/>
+  <dimension ref="A1:B418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13937,6 +14009,36 @@
       </c>
       <c r="B415" t="n">
         <v>-0.96</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -14105,28 +14207,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03618378229294905</v>
+        <v>0.02456448869058063</v>
       </c>
       <c r="J2" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K2" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005945041904207526</v>
+        <v>0.002694831734538994</v>
       </c>
       <c r="M2" t="n">
-        <v>2.870381967609242</v>
+        <v>2.904022557277824</v>
       </c>
       <c r="N2" t="n">
-        <v>12.37963581179123</v>
+        <v>12.74241115128973</v>
       </c>
       <c r="O2" t="n">
-        <v>3.518470663767318</v>
+        <v>3.569651404729842</v>
       </c>
       <c r="P2" t="n">
-        <v>368.0630200351598</v>
+        <v>368.1875826499224</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14183,28 +14285,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02668652914187647</v>
+        <v>0.02127633346045943</v>
       </c>
       <c r="J3" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K3" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00405285736931893</v>
+        <v>0.002597107553233391</v>
       </c>
       <c r="M3" t="n">
-        <v>2.60427837131423</v>
+        <v>2.609737424778692</v>
       </c>
       <c r="N3" t="n">
-        <v>9.91962364174015</v>
+        <v>9.94284804488553</v>
       </c>
       <c r="O3" t="n">
-        <v>3.149543402104526</v>
+        <v>3.153228194229769</v>
       </c>
       <c r="P3" t="n">
-        <v>376.9292563535164</v>
+        <v>376.9872125403477</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14261,28 +14363,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06674043710193092</v>
+        <v>0.06295047275822473</v>
       </c>
       <c r="J4" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02350051756153781</v>
+        <v>0.02120977507842692</v>
       </c>
       <c r="M4" t="n">
-        <v>2.401272813001441</v>
+        <v>2.40265072018857</v>
       </c>
       <c r="N4" t="n">
-        <v>10.46639577905257</v>
+        <v>10.43497210401444</v>
       </c>
       <c r="O4" t="n">
-        <v>3.235180949970584</v>
+        <v>3.230320743210253</v>
       </c>
       <c r="P4" t="n">
-        <v>384.8220065577341</v>
+        <v>384.8626390014123</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14339,28 +14441,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05884423973049724</v>
+        <v>0.05903902815854323</v>
       </c>
       <c r="J5" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K5" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01617803150996089</v>
+        <v>0.0165523521718034</v>
       </c>
       <c r="M5" t="n">
-        <v>2.614888170124066</v>
+        <v>2.597226925320056</v>
       </c>
       <c r="N5" t="n">
-        <v>11.90757212752555</v>
+        <v>11.81706618359262</v>
       </c>
       <c r="O5" t="n">
-        <v>3.450735012649559</v>
+        <v>3.437595989000543</v>
       </c>
       <c r="P5" t="n">
-        <v>386.5921908089673</v>
+        <v>386.5900987657128</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14398,7 +14500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F389"/>
+  <dimension ref="A1:F392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26845,6 +26947,102 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>-35.42906232724379,174.43145883171516</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>-35.429770780210895,174.43127838700485</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-35.430463691083375,174.4312040821098</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-35.431141094291654,174.4313577090409</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-35.42906359317015,174.43146295699026</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-35.429770780210895,174.43127838700485</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-35.430463733714895,174.43120573345135</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-35.43114050320626,174.4313628352385</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-35.42906470085559,174.43146656660602</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-35.42977003483238,174.43127521068368</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-35.4304636058203,174.43120077942666</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-35.431140151070174,174.43136588914345</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0071/nzd0071.xlsx
+++ b/data/nzd0071/nzd0071.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F392"/>
+  <dimension ref="A1:F394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9840,6 +9840,54 @@
         <v>388.65</v>
       </c>
       <c r="F392" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>362.47</v>
+      </c>
+      <c r="C393" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="D393" t="n">
+        <v>384.17</v>
+      </c>
+      <c r="E393" t="n">
+        <v>389.17</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="C394" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="D394" t="n">
+        <v>384.17</v>
+      </c>
+      <c r="E394" t="n">
+        <v>390.45</v>
+      </c>
+      <c r="F394" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9856,7 +9904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B418"/>
+  <dimension ref="A1:B420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14039,6 +14087,26 @@
       </c>
       <c r="B418" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -14207,28 +14275,28 @@
         <v>0.095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02456448869058063</v>
+        <v>0.01873294779729218</v>
       </c>
       <c r="J2" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K2" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002694831734538994</v>
+        <v>0.001564592346779081</v>
       </c>
       <c r="M2" t="n">
-        <v>2.904022557277824</v>
+        <v>2.917345867767327</v>
       </c>
       <c r="N2" t="n">
-        <v>12.74241115128973</v>
+        <v>12.85440846292362</v>
       </c>
       <c r="O2" t="n">
-        <v>3.569651404729842</v>
+        <v>3.585304514671469</v>
       </c>
       <c r="P2" t="n">
-        <v>368.1875826499224</v>
+        <v>368.2503639757808</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14285,28 +14353,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02127633346045943</v>
+        <v>0.01894902723895946</v>
       </c>
       <c r="J3" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K3" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002597107553233391</v>
+        <v>0.002078060139938831</v>
       </c>
       <c r="M3" t="n">
-        <v>2.609737424778692</v>
+        <v>2.607293420913169</v>
       </c>
       <c r="N3" t="n">
-        <v>9.94284804488553</v>
+        <v>9.920198968992306</v>
       </c>
       <c r="O3" t="n">
-        <v>3.153228194229769</v>
+        <v>3.149634735805456</v>
       </c>
       <c r="P3" t="n">
-        <v>376.9872125403477</v>
+        <v>377.0122493192066</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14363,28 +14431,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06295047275822473</v>
+        <v>0.06059236672403973</v>
       </c>
       <c r="J4" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K4" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02120977507842692</v>
+        <v>0.0198416222732466</v>
       </c>
       <c r="M4" t="n">
-        <v>2.40265072018857</v>
+        <v>2.40267269254038</v>
       </c>
       <c r="N4" t="n">
-        <v>10.43497210401444</v>
+        <v>10.41060548298739</v>
       </c>
       <c r="O4" t="n">
-        <v>3.230320743210253</v>
+        <v>3.226546990667793</v>
       </c>
       <c r="P4" t="n">
-        <v>384.8626390014123</v>
+        <v>384.8880268828901</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14441,28 +14509,28 @@
         <v>0.1102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05903902815854323</v>
+        <v>0.06063924839781765</v>
       </c>
       <c r="J5" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K5" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0165523521718034</v>
+        <v>0.01761376363504008</v>
       </c>
       <c r="M5" t="n">
-        <v>2.597226925320056</v>
+        <v>2.592117728423853</v>
       </c>
       <c r="N5" t="n">
-        <v>11.81706618359262</v>
+        <v>11.77223172729908</v>
       </c>
       <c r="O5" t="n">
-        <v>3.437595989000543</v>
+        <v>3.43106859845429</v>
       </c>
       <c r="P5" t="n">
-        <v>386.5900987657128</v>
+        <v>386.5728672405265</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14500,7 +14568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F392"/>
+  <dimension ref="A1:F394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27043,6 +27111,70 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-35.42906748589278,174.4314756422119</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-35.42977348841882,174.43128992763891</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-35.43046370529389,174.43120463255698</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-35.431139497102954,174.43137156068107</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-35.42907039752182,174.43148513034592</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-35.42977348841882,174.43128992763891</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-35.43046370529389,174.43120463255698</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-35.43113788733638,174.4313855213887</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
